--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОБЩИНА ВАРНА % 5 - ПДГ/ОБЩИНА ВАРНА % 5 - ПДГ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="37">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,10 +55,16 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Евkсиноград</t>
   </si>
   <si>
     <t>В2764ТА</t>
@@ -76,34 +79,28 @@
     <t>78970155027721996</t>
   </si>
   <si>
+    <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>10:48:00</t>
-  </si>
-  <si>
-    <t>11:06:00</t>
-  </si>
-  <si>
-    <t>07:29:00</t>
-  </si>
-  <si>
-    <t>15:44:00</t>
-  </si>
-  <si>
-    <t>3236492437 3236492437</t>
-  </si>
-  <si>
-    <t>3236639843 3236639843</t>
-  </si>
-  <si>
-    <t>3236957825 3236957825</t>
-  </si>
-  <si>
-    <t>3237221728 3237221728</t>
+    <t>13:57</t>
+  </si>
+  <si>
+    <t>11:56</t>
+  </si>
+  <si>
+    <t>07:47</t>
+  </si>
+  <si>
+    <t>16:26</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>10:59</t>
   </si>
   <si>
     <t>Забележка:</t>
@@ -538,7 +535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -547,17 +544,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -597,145 +593,133 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>22.33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>21</v>
+        <v>12</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.58</v>
       </c>
       <c r="H2" s="1">
-        <v>0.65</v>
+        <v>18.96</v>
       </c>
       <c r="I2" s="1">
-        <v>14.514</v>
+        <v>1.61</v>
       </c>
       <c r="J2" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K2" s="1">
-        <v>14.738</v>
-      </c>
-      <c r="L2" t="s">
-        <v>22</v>
+        <v>19.32</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2">
+        <v>61160</v>
       </c>
       <c r="M2">
-        <v>60720</v>
-      </c>
-      <c r="N2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+        <v>254386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
-        <v>46254</v>
+        <v>46267</v>
       </c>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3">
+        <v>25.52</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H3" s="1">
+        <v>16.588</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J3" s="1">
+        <v>16.843</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3">
+        <v>61200</v>
+      </c>
+      <c r="M3">
+        <v>169748</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46274</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" t="s">
+      <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>28.42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I3" s="1">
-        <v>18.473</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K3" s="1">
-        <v>18.757</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3">
-        <v>60980</v>
-      </c>
-      <c r="N3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46260</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4">
         <v>30</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
+      <c r="G4" s="1">
+        <v>0.66</v>
       </c>
       <c r="H4" s="1">
-        <v>0.65</v>
+        <v>19.8</v>
       </c>
       <c r="I4" s="1">
-        <v>19.5</v>
+        <v>0.67</v>
       </c>
       <c r="J4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="K4" s="1">
-        <v>19.8</v>
-      </c>
-      <c r="L4" t="s">
-        <v>24</v>
+        <v>20.1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4">
+        <v>63080</v>
       </c>
       <c r="M4">
-        <v>62400</v>
-      </c>
-      <c r="N4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+        <v>257428</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" s="3">
-        <v>46265</v>
+        <v>46274</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
@@ -747,131 +731,230 @@
         <v>19</v>
       </c>
       <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5">
+        <v>26.49</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H5" s="1">
+        <v>17.483</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J5" s="1">
+        <v>17.748</v>
+      </c>
+      <c r="K5" t="s">
+        <v>26</v>
+      </c>
+      <c r="L5">
+        <v>61460</v>
+      </c>
+      <c r="M5">
+        <v>299870</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="3">
+        <v>46275</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="F5">
-        <v>25.92</v>
-      </c>
-      <c r="G5" t="s">
+      <c r="E6" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="I5" s="1">
-        <v>16.848</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="F6">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="H6" s="1">
+        <v>19.2</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.63</v>
+      </c>
+      <c r="J6" s="1">
+        <v>19.56</v>
+      </c>
+      <c r="K6" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6">
+        <v>63200</v>
+      </c>
+      <c r="M6">
+        <v>258158</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="3">
+        <v>46280</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7">
+        <v>27.66</v>
+      </c>
+      <c r="G7" s="1">
         <v>0.66</v>
       </c>
-      <c r="K5" s="1">
-        <v>17.107</v>
-      </c>
-      <c r="L5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M5">
-        <v>62720</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="H7" s="1">
+        <v>18.256</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J7" s="1">
+        <v>18.532</v>
+      </c>
+      <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7">
+        <v>61720</v>
+      </c>
+      <c r="M7">
+        <v>152860</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
+    <row r="11" spans="1:13" ht="25" customHeight="1">
+      <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" ht="25" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" spans="1:13" ht="25" customHeight="1">
+      <c r="A12" s="5"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:14" ht="25" customHeight="1">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="6" t="s">
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="7" t="s">
+      <c r="B15" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C15" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="D15" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="E15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="9">
+        <v>109.67</v>
+      </c>
+      <c r="C16" s="10">
+        <v>4</v>
+      </c>
+      <c r="D16" s="11">
+        <v>0.65767</v>
+      </c>
+      <c r="E16" s="9">
+        <v>72.13</v>
+      </c>
+      <c r="F16" s="9">
+        <v>73.22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="9">
+        <v>24</v>
+      </c>
+      <c r="C17" s="10">
+        <v>2</v>
+      </c>
+      <c r="D17" s="11">
+        <v>1.59</v>
+      </c>
+      <c r="E17" s="9">
+        <v>38.16</v>
+      </c>
+      <c r="F17" s="9">
+        <v>38.88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="9">
-        <v>106.67</v>
-      </c>
-      <c r="C14" s="10">
-        <v>4</v>
-      </c>
-      <c r="D14" s="11">
-        <v>0.65</v>
-      </c>
-      <c r="E14" s="9">
-        <v>69.33</v>
-      </c>
-      <c r="F14" s="9">
-        <v>70.40000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B15" s="13">
-        <v>106.67</v>
-      </c>
-      <c r="C15" s="14">
-        <v>4</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="13">
-        <v>69.33</v>
-      </c>
-      <c r="F15" s="13">
-        <v>70.40000000000001</v>
+      <c r="B18" s="13">
+        <v>133.67</v>
+      </c>
+      <c r="C18" s="14">
+        <v>6</v>
+      </c>
+      <c r="D18" s="11"/>
+      <c r="E18" s="13">
+        <v>110.29</v>
+      </c>
+      <c r="F18" s="13">
+        <v>112.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:F10"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A11:F12"/>
+    <mergeCell ref="A14:F14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
